--- a/AKTIVITAS KERJAKU.xlsx
+++ b/AKTIVITAS KERJAKU.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="193" documentId="8_{848DFA7F-C708-4B3A-A593-29E660D4EA5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{516771C9-6675-4F01-8D2B-25008D22B5D1}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{E2C05058-1B23-4DD0-A60D-DB7A4B1DBCD6}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{E2C05058-1B23-4DD0-A60D-DB7A4B1DBCD6}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -975,20 +975,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B4CB50E-74A1-4CEE-9516-E4C7B033C8ED}">
   <dimension ref="A1:J24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.140625" customWidth="1"/>
-    <col min="2" max="3" width="15.28515625" customWidth="1"/>
-    <col min="4" max="4" width="26.28515625" customWidth="1"/>
-    <col min="5" max="5" width="34.28515625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="14.109375" customWidth="1"/>
+    <col min="2" max="3" width="15.33203125" customWidth="1"/>
+    <col min="4" max="4" width="26.33203125" customWidth="1"/>
+    <col min="5" max="5" width="34.33203125" style="5" customWidth="1"/>
     <col min="6" max="6" width="12" style="5" customWidth="1"/>
-    <col min="7" max="7" width="10.28515625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="9.85546875" customWidth="1"/>
-    <col min="9" max="9" width="12.140625" customWidth="1"/>
-    <col min="10" max="10" width="31.5703125" customWidth="1"/>
+    <col min="7" max="7" width="10.33203125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="9.88671875" customWidth="1"/>
+    <col min="9" max="9" width="12.109375" customWidth="1"/>
+    <col min="10" max="10" width="31.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="13" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="13" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1020,7 +1020,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>79</v>
       </c>
@@ -1050,7 +1050,7 @@
       <c r="I2" s="5"/>
       <c r="J2" s="5"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>79</v>
       </c>
@@ -1080,7 +1080,7 @@
       <c r="I3" s="5"/>
       <c r="J3" s="5"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>79</v>
       </c>
@@ -1110,7 +1110,7 @@
       <c r="I4" s="5"/>
       <c r="J4" s="5"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>79</v>
       </c>
@@ -1140,7 +1140,7 @@
       <c r="I5" s="5"/>
       <c r="J5" s="5"/>
     </row>
-    <row r="6" spans="1:10" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>79</v>
       </c>
@@ -1170,7 +1170,7 @@
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
     </row>
-    <row r="7" spans="1:10" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>80</v>
       </c>
@@ -1200,7 +1200,7 @@
       <c r="I7" s="5"/>
       <c r="J7" s="9"/>
     </row>
-    <row r="8" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>80</v>
       </c>
@@ -1230,7 +1230,7 @@
       <c r="I8" s="5"/>
       <c r="J8" s="9"/>
     </row>
-    <row r="9" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>80</v>
       </c>
@@ -1260,7 +1260,7 @@
       <c r="I9" s="5"/>
       <c r="J9" s="9"/>
     </row>
-    <row r="10" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>80</v>
       </c>
@@ -1290,7 +1290,7 @@
       <c r="I10" s="5"/>
       <c r="J10" s="9"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>81</v>
       </c>
@@ -1320,7 +1320,7 @@
       <c r="I11" s="5"/>
       <c r="J11" s="9"/>
     </row>
-    <row r="12" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>81</v>
       </c>
@@ -1350,7 +1350,7 @@
       <c r="I12" s="5"/>
       <c r="J12" s="9"/>
     </row>
-    <row r="13" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>81</v>
       </c>
@@ -1380,7 +1380,7 @@
       <c r="I13" s="5"/>
       <c r="J13" s="9"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>82</v>
       </c>
@@ -1410,7 +1410,7 @@
       <c r="I14" s="5"/>
       <c r="J14" s="9"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>82</v>
       </c>
@@ -1440,7 +1440,7 @@
       <c r="I15" s="5"/>
       <c r="J15" s="9"/>
     </row>
-    <row r="16" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>82</v>
       </c>
@@ -1470,7 +1470,7 @@
       <c r="I16" s="5"/>
       <c r="J16" s="9"/>
     </row>
-    <row r="17" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>83</v>
       </c>
@@ -1500,7 +1500,7 @@
       <c r="I17" s="5"/>
       <c r="J17" s="9"/>
     </row>
-    <row r="18" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>83</v>
       </c>
@@ -1530,7 +1530,7 @@
       <c r="I18" s="5"/>
       <c r="J18" s="9"/>
     </row>
-    <row r="19" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>83</v>
       </c>
@@ -1560,7 +1560,7 @@
       <c r="I19" s="5"/>
       <c r="J19" s="9"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="4"/>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
@@ -1569,7 +1569,7 @@
       <c r="I20" s="5"/>
       <c r="J20" s="9"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="4"/>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
@@ -1578,7 +1578,7 @@
       <c r="I21" s="5"/>
       <c r="J21" s="9"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="4"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
@@ -1587,7 +1587,7 @@
       <c r="I22" s="5"/>
       <c r="J22" s="9"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="4"/>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -1596,7 +1596,7 @@
       <c r="I23" s="5"/>
       <c r="J23" s="9"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="4"/>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
@@ -1630,17 +1630,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F14D1DC-483D-444F-80D4-8DE5D79B7A1F}">
   <dimension ref="A1:L31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="84.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.7109375" customWidth="1"/>
-    <col min="3" max="3" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="73.140625" customWidth="1"/>
-    <col min="11" max="11" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="84.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.6640625" customWidth="1"/>
+    <col min="3" max="3" width="20.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="73.109375" customWidth="1"/>
+    <col min="11" max="11" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>27</v>
       </c>
@@ -1651,7 +1651,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>22</v>
       </c>
@@ -1663,7 +1663,7 @@
       </c>
       <c r="L2" s="7"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="L3" s="7"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -1687,7 +1687,7 @@
       </c>
       <c r="L4" s="7"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="L5" s="7"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="L6" s="7"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -1722,7 +1722,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -1733,7 +1733,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>32</v>
       </c>
@@ -1744,7 +1744,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>85</v>
       </c>
@@ -1759,7 +1759,7 @@
       <c r="K10" s="10"/>
       <c r="L10" s="11"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>86</v>
       </c>
@@ -1774,7 +1774,7 @@
       <c r="K11" s="10"/>
       <c r="L11" s="11"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>87</v>
       </c>
@@ -1785,7 +1785,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>88</v>
       </c>
@@ -1796,7 +1796,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>89</v>
       </c>
@@ -1807,7 +1807,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>90</v>
       </c>
@@ -1818,7 +1818,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>91</v>
       </c>
@@ -1829,7 +1829,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>92</v>
       </c>
@@ -1840,7 +1840,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>93</v>
       </c>
@@ -1851,7 +1851,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>94</v>
       </c>
@@ -1862,7 +1862,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>95</v>
       </c>
@@ -1873,7 +1873,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>96</v>
       </c>
@@ -1884,7 +1884,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>97</v>
       </c>
@@ -1895,7 +1895,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>98</v>
       </c>
@@ -1906,7 +1906,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>99</v>
       </c>
@@ -1917,7 +1917,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>100</v>
       </c>
@@ -1928,7 +1928,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>101</v>
       </c>
@@ -1939,7 +1939,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>102</v>
       </c>
@@ -1950,7 +1950,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>103</v>
       </c>
@@ -1961,7 +1961,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>105</v>
       </c>
@@ -1972,7 +1972,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>107</v>
       </c>
@@ -1983,7 +1983,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>108</v>
       </c>
@@ -2006,15 +2006,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5268B04A-DFEF-46BB-92FA-CECB83088F66}">
   <dimension ref="A1:BF139"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:58" x14ac:dyDescent="0.3">
       <c r="J1" s="7"/>
       <c r="K1" s="7"/>
       <c r="L1" s="7"/>
@@ -2065,7 +2065,7 @@
       <c r="BE1" s="7"/>
       <c r="BF1" s="7"/>
     </row>
-    <row r="2" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>109</v>
       </c>
@@ -2140,7 +2140,7 @@
       <c r="BE2" s="7"/>
       <c r="BF2" s="7"/>
     </row>
-    <row r="3" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>112</v>
       </c>
@@ -2215,7 +2215,7 @@
       <c r="BE3" s="7"/>
       <c r="BF3" s="7"/>
     </row>
-    <row r="4" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>115</v>
       </c>
@@ -2290,7 +2290,7 @@
       <c r="BE4" s="7"/>
       <c r="BF4" s="7"/>
     </row>
-    <row r="5" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>118</v>
       </c>
@@ -2365,7 +2365,7 @@
       <c r="BE5" s="7"/>
       <c r="BF5" s="7"/>
     </row>
-    <row r="6" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>121</v>
       </c>
@@ -2440,7 +2440,7 @@
       <c r="BE6" s="7"/>
       <c r="BF6" s="7"/>
     </row>
-    <row r="7" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>41</v>
       </c>
@@ -2515,7 +2515,7 @@
       <c r="BE7" s="7"/>
       <c r="BF7" s="7"/>
     </row>
-    <row r="8" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>42</v>
       </c>
@@ -2590,7 +2590,7 @@
       <c r="BE8" s="7"/>
       <c r="BF8" s="7"/>
     </row>
-    <row r="9" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
         <v>43</v>
       </c>
@@ -2665,7 +2665,7 @@
       <c r="BE9" s="7"/>
       <c r="BF9" s="7"/>
     </row>
-    <row r="10" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>45</v>
       </c>
@@ -2740,7 +2740,7 @@
       <c r="BE10" s="7"/>
       <c r="BF10" s="7"/>
     </row>
-    <row r="11" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>46</v>
       </c>
@@ -2812,7 +2812,7 @@
       <c r="BE11" s="7"/>
       <c r="BF11" s="7"/>
     </row>
-    <row r="12" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>47</v>
       </c>
@@ -2884,7 +2884,7 @@
       <c r="BE12" s="7"/>
       <c r="BF12" s="7"/>
     </row>
-    <row r="13" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>48</v>
       </c>
@@ -2956,7 +2956,7 @@
       <c r="BE13" s="7"/>
       <c r="BF13" s="7"/>
     </row>
-    <row r="14" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
         <v>49</v>
       </c>
@@ -3028,7 +3028,7 @@
       <c r="BE14" s="7"/>
       <c r="BF14" s="7"/>
     </row>
-    <row r="15" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>50</v>
       </c>
@@ -3100,7 +3100,7 @@
       <c r="BE15" s="7"/>
       <c r="BF15" s="7"/>
     </row>
-    <row r="16" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
         <v>51</v>
       </c>
@@ -3172,7 +3172,7 @@
       <c r="BE16" s="7"/>
       <c r="BF16" s="7"/>
     </row>
-    <row r="17" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
         <v>52</v>
       </c>
@@ -3244,7 +3244,7 @@
       <c r="BE17" s="7"/>
       <c r="BF17" s="7"/>
     </row>
-    <row r="18" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
         <v>53</v>
       </c>
@@ -3316,7 +3316,7 @@
       <c r="BE18" s="7"/>
       <c r="BF18" s="7"/>
     </row>
-    <row r="19" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
         <v>54</v>
       </c>
@@ -3388,7 +3388,7 @@
       <c r="BE19" s="7"/>
       <c r="BF19" s="7"/>
     </row>
-    <row r="20" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
         <v>55</v>
       </c>
@@ -3460,7 +3460,7 @@
       <c r="BE20" s="7"/>
       <c r="BF20" s="7"/>
     </row>
-    <row r="21" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
         <v>56</v>
       </c>
@@ -3532,7 +3532,7 @@
       <c r="BE21" s="7"/>
       <c r="BF21" s="7"/>
     </row>
-    <row r="22" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>57</v>
       </c>
@@ -3604,7 +3604,7 @@
       <c r="BE22" s="7"/>
       <c r="BF22" s="7"/>
     </row>
-    <row r="23" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:58" x14ac:dyDescent="0.3">
       <c r="J23" s="7"/>
       <c r="K23" s="7"/>
       <c r="L23" s="7"/>
@@ -3655,7 +3655,7 @@
       <c r="BE23" s="7"/>
       <c r="BF23" s="7"/>
     </row>
-    <row r="24" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>109</v>
       </c>
@@ -3715,7 +3715,7 @@
       <c r="BE24" s="7"/>
       <c r="BF24" s="7"/>
     </row>
-    <row r="25" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>112</v>
       </c>
@@ -3775,7 +3775,7 @@
       <c r="BE25" s="7"/>
       <c r="BF25" s="7"/>
     </row>
-    <row r="26" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>115</v>
       </c>
@@ -3835,7 +3835,7 @@
       <c r="BE26" s="7"/>
       <c r="BF26" s="7"/>
     </row>
-    <row r="27" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>118</v>
       </c>
@@ -3895,7 +3895,7 @@
       <c r="BE27" s="7"/>
       <c r="BF27" s="7"/>
     </row>
-    <row r="28" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>121</v>
       </c>
@@ -3952,7 +3952,7 @@
       <c r="BE28" s="7"/>
       <c r="BF28" s="7"/>
     </row>
-    <row r="29" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:58" x14ac:dyDescent="0.3">
       <c r="J29" s="7"/>
       <c r="K29" s="7"/>
       <c r="O29" s="7"/>
@@ -4000,7 +4000,7 @@
       <c r="BE29" s="7"/>
       <c r="BF29" s="7"/>
     </row>
-    <row r="30" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:58" x14ac:dyDescent="0.3">
       <c r="J30" s="7"/>
       <c r="K30" s="7"/>
       <c r="L30" s="7"/>
@@ -4051,7 +4051,7 @@
       <c r="BE30" s="7"/>
       <c r="BF30" s="7"/>
     </row>
-    <row r="31" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:58" x14ac:dyDescent="0.3">
       <c r="J31" s="7"/>
       <c r="K31" s="7"/>
       <c r="L31" s="7"/>
@@ -4102,7 +4102,7 @@
       <c r="BE31" s="7"/>
       <c r="BF31" s="7"/>
     </row>
-    <row r="32" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:58" x14ac:dyDescent="0.3">
       <c r="J32" s="7"/>
       <c r="K32" s="7"/>
       <c r="L32" s="7"/>
@@ -4153,7 +4153,7 @@
       <c r="BE32" s="7"/>
       <c r="BF32" s="7"/>
     </row>
-    <row r="33" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="33" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J33" s="7"/>
       <c r="K33" s="7"/>
       <c r="L33" s="7"/>
@@ -4204,7 +4204,7 @@
       <c r="BE33" s="7"/>
       <c r="BF33" s="7"/>
     </row>
-    <row r="34" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="34" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J34" s="7"/>
       <c r="K34" s="7"/>
       <c r="L34" s="7"/>
@@ -4255,7 +4255,7 @@
       <c r="BE34" s="7"/>
       <c r="BF34" s="7"/>
     </row>
-    <row r="35" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="35" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J35" s="7"/>
       <c r="K35" s="7"/>
       <c r="L35" s="7"/>
@@ -4306,7 +4306,7 @@
       <c r="BE35" s="7"/>
       <c r="BF35" s="7"/>
     </row>
-    <row r="36" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="36" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J36" s="7"/>
       <c r="K36" s="7"/>
       <c r="L36" s="7"/>
@@ -4357,7 +4357,7 @@
       <c r="BE36" s="7"/>
       <c r="BF36" s="7"/>
     </row>
-    <row r="37" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="37" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J37" s="7"/>
       <c r="K37" s="7"/>
       <c r="L37" s="7"/>
@@ -4408,7 +4408,7 @@
       <c r="BE37" s="7"/>
       <c r="BF37" s="7"/>
     </row>
-    <row r="38" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="38" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J38" s="7"/>
       <c r="K38" s="7"/>
       <c r="L38" s="7"/>
@@ -4459,7 +4459,7 @@
       <c r="BE38" s="7"/>
       <c r="BF38" s="7"/>
     </row>
-    <row r="39" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="39" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J39" s="7"/>
       <c r="K39" s="7"/>
       <c r="L39" s="7"/>
@@ -4510,7 +4510,7 @@
       <c r="BE39" s="7"/>
       <c r="BF39" s="7"/>
     </row>
-    <row r="40" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="40" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J40" s="7"/>
       <c r="K40" s="7"/>
       <c r="L40" s="7"/>
@@ -4561,7 +4561,7 @@
       <c r="BE40" s="7"/>
       <c r="BF40" s="7"/>
     </row>
-    <row r="41" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="41" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J41" s="7"/>
       <c r="K41" s="7"/>
       <c r="L41" s="7"/>
@@ -4612,7 +4612,7 @@
       <c r="BE41" s="7"/>
       <c r="BF41" s="7"/>
     </row>
-    <row r="42" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="42" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J42" s="7"/>
       <c r="K42" s="7"/>
       <c r="L42" s="7"/>
@@ -4663,7 +4663,7 @@
       <c r="BE42" s="7"/>
       <c r="BF42" s="7"/>
     </row>
-    <row r="43" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="43" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J43" s="7"/>
       <c r="K43" s="7"/>
       <c r="L43" s="7"/>
@@ -4714,7 +4714,7 @@
       <c r="BE43" s="7"/>
       <c r="BF43" s="7"/>
     </row>
-    <row r="44" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="44" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J44" s="7"/>
       <c r="K44" s="7"/>
       <c r="L44" s="7"/>
@@ -4765,7 +4765,7 @@
       <c r="BE44" s="7"/>
       <c r="BF44" s="7"/>
     </row>
-    <row r="45" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="45" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J45" s="7"/>
       <c r="K45" s="7"/>
       <c r="L45" s="7"/>
@@ -4816,7 +4816,7 @@
       <c r="BE45" s="7"/>
       <c r="BF45" s="7"/>
     </row>
-    <row r="46" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="46" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J46" s="7"/>
       <c r="K46" s="7"/>
       <c r="L46" s="7"/>
@@ -4867,7 +4867,7 @@
       <c r="BE46" s="7"/>
       <c r="BF46" s="7"/>
     </row>
-    <row r="47" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="47" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J47" s="7"/>
       <c r="K47" s="7"/>
       <c r="L47" s="7"/>
@@ -4918,7 +4918,7 @@
       <c r="BE47" s="7"/>
       <c r="BF47" s="7"/>
     </row>
-    <row r="48" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="48" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J48" s="7"/>
       <c r="K48" s="7"/>
       <c r="L48" s="7"/>
@@ -4969,7 +4969,7 @@
       <c r="BE48" s="7"/>
       <c r="BF48" s="7"/>
     </row>
-    <row r="49" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="49" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J49" s="7"/>
       <c r="K49" s="7"/>
       <c r="L49" s="7"/>
@@ -5020,7 +5020,7 @@
       <c r="BE49" s="7"/>
       <c r="BF49" s="7"/>
     </row>
-    <row r="50" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="50" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J50" s="7"/>
       <c r="K50" s="7"/>
       <c r="L50" s="7"/>
@@ -5071,7 +5071,7 @@
       <c r="BE50" s="7"/>
       <c r="BF50" s="7"/>
     </row>
-    <row r="51" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="51" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J51" s="7"/>
       <c r="K51" s="7"/>
       <c r="L51" s="7"/>
@@ -5122,7 +5122,7 @@
       <c r="BE51" s="7"/>
       <c r="BF51" s="7"/>
     </row>
-    <row r="52" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="52" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J52" s="7"/>
       <c r="K52" s="7"/>
       <c r="L52" s="7"/>
@@ -5173,7 +5173,7 @@
       <c r="BE52" s="7"/>
       <c r="BF52" s="7"/>
     </row>
-    <row r="53" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="53" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J53" s="7"/>
       <c r="K53" s="7"/>
       <c r="L53" s="7"/>
@@ -5224,7 +5224,7 @@
       <c r="BE53" s="7"/>
       <c r="BF53" s="7"/>
     </row>
-    <row r="54" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="54" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J54" s="7"/>
       <c r="K54" s="7"/>
       <c r="L54" s="7"/>
@@ -5275,7 +5275,7 @@
       <c r="BE54" s="7"/>
       <c r="BF54" s="7"/>
     </row>
-    <row r="55" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="55" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J55" s="7"/>
       <c r="K55" s="7"/>
       <c r="L55" s="7"/>
@@ -5326,7 +5326,7 @@
       <c r="BE55" s="7"/>
       <c r="BF55" s="7"/>
     </row>
-    <row r="56" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="56" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J56" s="7"/>
       <c r="K56" s="7"/>
       <c r="L56" s="7"/>
@@ -5377,7 +5377,7 @@
       <c r="BE56" s="7"/>
       <c r="BF56" s="7"/>
     </row>
-    <row r="57" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="57" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J57" s="7"/>
       <c r="K57" s="7"/>
       <c r="L57" s="7"/>
@@ -5428,7 +5428,7 @@
       <c r="BE57" s="7"/>
       <c r="BF57" s="7"/>
     </row>
-    <row r="58" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="58" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J58" s="7"/>
       <c r="K58" s="7"/>
       <c r="L58" s="7"/>
@@ -5479,7 +5479,7 @@
       <c r="BE58" s="7"/>
       <c r="BF58" s="7"/>
     </row>
-    <row r="59" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="59" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J59" s="7"/>
       <c r="K59" s="7"/>
       <c r="L59" s="7"/>
@@ -5530,7 +5530,7 @@
       <c r="BE59" s="7"/>
       <c r="BF59" s="7"/>
     </row>
-    <row r="60" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="60" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J60" s="7"/>
       <c r="K60" s="7"/>
       <c r="L60" s="7"/>
@@ -5581,7 +5581,7 @@
       <c r="BE60" s="7"/>
       <c r="BF60" s="7"/>
     </row>
-    <row r="61" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="61" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J61" s="7"/>
       <c r="K61" s="7"/>
       <c r="L61" s="7"/>
@@ -5632,7 +5632,7 @@
       <c r="BE61" s="7"/>
       <c r="BF61" s="7"/>
     </row>
-    <row r="62" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="62" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J62" s="7"/>
       <c r="K62" s="7"/>
       <c r="L62" s="7"/>
@@ -5683,7 +5683,7 @@
       <c r="BE62" s="7"/>
       <c r="BF62" s="7"/>
     </row>
-    <row r="63" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="63" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J63" s="7"/>
       <c r="K63" s="7"/>
       <c r="L63" s="7"/>
@@ -5734,7 +5734,7 @@
       <c r="BE63" s="7"/>
       <c r="BF63" s="7"/>
     </row>
-    <row r="64" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="64" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J64" s="7"/>
       <c r="K64" s="7"/>
       <c r="L64" s="7"/>
@@ -5785,7 +5785,7 @@
       <c r="BE64" s="7"/>
       <c r="BF64" s="7"/>
     </row>
-    <row r="65" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="65" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J65" s="7"/>
       <c r="K65" s="7"/>
       <c r="L65" s="7"/>
@@ -5836,7 +5836,7 @@
       <c r="BE65" s="7"/>
       <c r="BF65" s="7"/>
     </row>
-    <row r="66" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="66" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J66" s="7"/>
       <c r="K66" s="7"/>
       <c r="L66" s="7"/>
@@ -5887,7 +5887,7 @@
       <c r="BE66" s="7"/>
       <c r="BF66" s="7"/>
     </row>
-    <row r="67" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="67" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J67" s="7"/>
       <c r="K67" s="7"/>
       <c r="L67" s="7"/>
@@ -5938,7 +5938,7 @@
       <c r="BE67" s="7"/>
       <c r="BF67" s="7"/>
     </row>
-    <row r="68" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="68" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J68" s="7"/>
       <c r="K68" s="7"/>
       <c r="L68" s="7"/>
@@ -5989,7 +5989,7 @@
       <c r="BE68" s="7"/>
       <c r="BF68" s="7"/>
     </row>
-    <row r="69" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="69" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J69" s="7"/>
       <c r="K69" s="7"/>
       <c r="L69" s="7"/>
@@ -6040,7 +6040,7 @@
       <c r="BE69" s="7"/>
       <c r="BF69" s="7"/>
     </row>
-    <row r="70" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="70" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J70" s="7"/>
       <c r="K70" s="7"/>
       <c r="L70" s="7"/>
@@ -6091,7 +6091,7 @@
       <c r="BE70" s="7"/>
       <c r="BF70" s="7"/>
     </row>
-    <row r="71" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="71" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J71" s="7"/>
       <c r="K71" s="7"/>
       <c r="L71" s="7"/>
@@ -6142,7 +6142,7 @@
       <c r="BE71" s="7"/>
       <c r="BF71" s="7"/>
     </row>
-    <row r="72" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="72" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J72" s="7"/>
       <c r="K72" s="7"/>
       <c r="L72" s="7"/>
@@ -6193,7 +6193,7 @@
       <c r="BE72" s="7"/>
       <c r="BF72" s="7"/>
     </row>
-    <row r="73" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="73" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J73" s="7"/>
       <c r="K73" s="7"/>
       <c r="L73" s="7"/>
@@ -6244,7 +6244,7 @@
       <c r="BE73" s="7"/>
       <c r="BF73" s="7"/>
     </row>
-    <row r="74" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="74" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J74" s="7"/>
       <c r="K74" s="7"/>
       <c r="L74" s="7"/>
@@ -6295,7 +6295,7 @@
       <c r="BE74" s="7"/>
       <c r="BF74" s="7"/>
     </row>
-    <row r="75" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="75" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J75" s="7"/>
       <c r="K75" s="7"/>
       <c r="L75" s="7"/>
@@ -6346,7 +6346,7 @@
       <c r="BE75" s="7"/>
       <c r="BF75" s="7"/>
     </row>
-    <row r="76" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="76" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J76" s="7"/>
       <c r="K76" s="7"/>
       <c r="L76" s="7"/>
@@ -6397,7 +6397,7 @@
       <c r="BE76" s="7"/>
       <c r="BF76" s="7"/>
     </row>
-    <row r="77" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="77" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J77" s="7"/>
       <c r="K77" s="7"/>
       <c r="L77" s="7"/>
@@ -6448,7 +6448,7 @@
       <c r="BE77" s="7"/>
       <c r="BF77" s="7"/>
     </row>
-    <row r="78" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="78" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J78" s="7"/>
       <c r="K78" s="7"/>
       <c r="L78" s="7"/>
@@ -6499,7 +6499,7 @@
       <c r="BE78" s="7"/>
       <c r="BF78" s="7"/>
     </row>
-    <row r="79" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="79" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J79" s="7"/>
       <c r="K79" s="7"/>
       <c r="L79" s="7"/>
@@ -6550,7 +6550,7 @@
       <c r="BE79" s="7"/>
       <c r="BF79" s="7"/>
     </row>
-    <row r="80" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="80" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J80" s="7"/>
       <c r="K80" s="7"/>
       <c r="L80" s="7"/>
@@ -6601,7 +6601,7 @@
       <c r="BE80" s="7"/>
       <c r="BF80" s="7"/>
     </row>
-    <row r="81" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="81" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J81" s="7"/>
       <c r="K81" s="7"/>
       <c r="L81" s="7"/>
@@ -6652,7 +6652,7 @@
       <c r="BE81" s="7"/>
       <c r="BF81" s="7"/>
     </row>
-    <row r="82" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="82" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J82" s="7"/>
       <c r="K82" s="7"/>
       <c r="L82" s="7"/>
@@ -6703,7 +6703,7 @@
       <c r="BE82" s="7"/>
       <c r="BF82" s="7"/>
     </row>
-    <row r="83" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="83" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J83" s="7"/>
       <c r="K83" s="7"/>
       <c r="L83" s="7"/>
@@ -6754,7 +6754,7 @@
       <c r="BE83" s="7"/>
       <c r="BF83" s="7"/>
     </row>
-    <row r="84" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="84" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J84" s="7"/>
       <c r="K84" s="7"/>
       <c r="L84" s="7"/>
@@ -6805,7 +6805,7 @@
       <c r="BE84" s="7"/>
       <c r="BF84" s="7"/>
     </row>
-    <row r="85" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="85" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J85" s="7"/>
       <c r="K85" s="7"/>
       <c r="L85" s="7"/>
@@ -6856,7 +6856,7 @@
       <c r="BE85" s="7"/>
       <c r="BF85" s="7"/>
     </row>
-    <row r="86" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="86" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J86" s="7"/>
       <c r="K86" s="7"/>
       <c r="L86" s="7"/>
@@ -6907,7 +6907,7 @@
       <c r="BE86" s="7"/>
       <c r="BF86" s="7"/>
     </row>
-    <row r="87" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="87" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J87" s="7"/>
       <c r="K87" s="7"/>
       <c r="L87" s="7"/>
@@ -6958,7 +6958,7 @@
       <c r="BE87" s="7"/>
       <c r="BF87" s="7"/>
     </row>
-    <row r="88" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="88" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J88" s="7"/>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
@@ -7009,7 +7009,7 @@
       <c r="BE88" s="7"/>
       <c r="BF88" s="7"/>
     </row>
-    <row r="89" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="89" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J89" s="7"/>
       <c r="K89" s="7"/>
       <c r="L89" s="7"/>
@@ -7060,7 +7060,7 @@
       <c r="BE89" s="7"/>
       <c r="BF89" s="7"/>
     </row>
-    <row r="90" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="90" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J90" s="7"/>
       <c r="K90" s="7"/>
       <c r="L90" s="7"/>
@@ -7111,7 +7111,7 @@
       <c r="BE90" s="7"/>
       <c r="BF90" s="7"/>
     </row>
-    <row r="91" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="91" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J91" s="7"/>
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
@@ -7162,7 +7162,7 @@
       <c r="BE91" s="7"/>
       <c r="BF91" s="7"/>
     </row>
-    <row r="92" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="92" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J92" s="7"/>
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
@@ -7213,7 +7213,7 @@
       <c r="BE92" s="7"/>
       <c r="BF92" s="7"/>
     </row>
-    <row r="93" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="93" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J93" s="7"/>
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
@@ -7264,7 +7264,7 @@
       <c r="BE93" s="7"/>
       <c r="BF93" s="7"/>
     </row>
-    <row r="94" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="94" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J94" s="7"/>
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
@@ -7315,7 +7315,7 @@
       <c r="BE94" s="7"/>
       <c r="BF94" s="7"/>
     </row>
-    <row r="95" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="95" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J95" s="7"/>
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
@@ -7366,7 +7366,7 @@
       <c r="BE95" s="7"/>
       <c r="BF95" s="7"/>
     </row>
-    <row r="96" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="96" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J96" s="7"/>
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
@@ -7417,7 +7417,7 @@
       <c r="BE96" s="7"/>
       <c r="BF96" s="7"/>
     </row>
-    <row r="97" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="97" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J97" s="7"/>
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
@@ -7468,7 +7468,7 @@
       <c r="BE97" s="7"/>
       <c r="BF97" s="7"/>
     </row>
-    <row r="98" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="98" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J98" s="7"/>
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
@@ -7519,7 +7519,7 @@
       <c r="BE98" s="7"/>
       <c r="BF98" s="7"/>
     </row>
-    <row r="99" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="99" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J99" s="7"/>
       <c r="K99" s="7"/>
       <c r="L99" s="7"/>
@@ -7570,7 +7570,7 @@
       <c r="BE99" s="7"/>
       <c r="BF99" s="7"/>
     </row>
-    <row r="100" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="100" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J100" s="7"/>
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
@@ -7621,7 +7621,7 @@
       <c r="BE100" s="7"/>
       <c r="BF100" s="7"/>
     </row>
-    <row r="101" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="101" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J101" s="7"/>
       <c r="K101" s="7"/>
       <c r="L101" s="7"/>
@@ -7672,7 +7672,7 @@
       <c r="BE101" s="7"/>
       <c r="BF101" s="7"/>
     </row>
-    <row r="102" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="102" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J102" s="7"/>
       <c r="K102" s="7"/>
       <c r="L102" s="7"/>
@@ -7723,7 +7723,7 @@
       <c r="BE102" s="7"/>
       <c r="BF102" s="7"/>
     </row>
-    <row r="103" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="103" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J103" s="7"/>
       <c r="K103" s="7"/>
       <c r="L103" s="7"/>
@@ -7774,7 +7774,7 @@
       <c r="BE103" s="7"/>
       <c r="BF103" s="7"/>
     </row>
-    <row r="104" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="104" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J104" s="7"/>
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
@@ -7825,7 +7825,7 @@
       <c r="BE104" s="7"/>
       <c r="BF104" s="7"/>
     </row>
-    <row r="105" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="105" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J105" s="7"/>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
@@ -7876,7 +7876,7 @@
       <c r="BE105" s="7"/>
       <c r="BF105" s="7"/>
     </row>
-    <row r="106" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="106" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J106" s="7"/>
       <c r="K106" s="7"/>
       <c r="L106" s="7"/>
@@ -7927,7 +7927,7 @@
       <c r="BE106" s="7"/>
       <c r="BF106" s="7"/>
     </row>
-    <row r="107" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="107" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J107" s="7"/>
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
@@ -7978,7 +7978,7 @@
       <c r="BE107" s="7"/>
       <c r="BF107" s="7"/>
     </row>
-    <row r="108" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="108" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J108" s="7"/>
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
@@ -8029,7 +8029,7 @@
       <c r="BE108" s="7"/>
       <c r="BF108" s="7"/>
     </row>
-    <row r="109" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="109" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J109" s="7"/>
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
@@ -8080,7 +8080,7 @@
       <c r="BE109" s="7"/>
       <c r="BF109" s="7"/>
     </row>
-    <row r="110" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="110" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J110" s="7"/>
       <c r="K110" s="7"/>
       <c r="L110" s="7"/>
@@ -8131,7 +8131,7 @@
       <c r="BE110" s="7"/>
       <c r="BF110" s="7"/>
     </row>
-    <row r="111" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="111" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J111" s="7"/>
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
@@ -8182,7 +8182,7 @@
       <c r="BE111" s="7"/>
       <c r="BF111" s="7"/>
     </row>
-    <row r="112" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="112" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J112" s="7"/>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
@@ -8233,7 +8233,7 @@
       <c r="BE112" s="7"/>
       <c r="BF112" s="7"/>
     </row>
-    <row r="113" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="113" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J113" s="7"/>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
@@ -8284,7 +8284,7 @@
       <c r="BE113" s="7"/>
       <c r="BF113" s="7"/>
     </row>
-    <row r="114" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="114" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J114" s="7"/>
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
@@ -8335,7 +8335,7 @@
       <c r="BE114" s="7"/>
       <c r="BF114" s="7"/>
     </row>
-    <row r="115" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="115" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J115" s="7"/>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
@@ -8386,7 +8386,7 @@
       <c r="BE115" s="7"/>
       <c r="BF115" s="7"/>
     </row>
-    <row r="116" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="116" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J116" s="7"/>
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
@@ -8437,7 +8437,7 @@
       <c r="BE116" s="7"/>
       <c r="BF116" s="7"/>
     </row>
-    <row r="117" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="117" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J117" s="7"/>
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
@@ -8488,7 +8488,7 @@
       <c r="BE117" s="7"/>
       <c r="BF117" s="7"/>
     </row>
-    <row r="118" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="118" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J118" s="7"/>
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
@@ -8539,7 +8539,7 @@
       <c r="BE118" s="7"/>
       <c r="BF118" s="7"/>
     </row>
-    <row r="119" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="119" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J119" s="7"/>
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
@@ -8590,7 +8590,7 @@
       <c r="BE119" s="7"/>
       <c r="BF119" s="7"/>
     </row>
-    <row r="120" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="120" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J120" s="7"/>
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
@@ -8641,7 +8641,7 @@
       <c r="BE120" s="7"/>
       <c r="BF120" s="7"/>
     </row>
-    <row r="121" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="121" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J121" s="7"/>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
@@ -8692,7 +8692,7 @@
       <c r="BE121" s="7"/>
       <c r="BF121" s="7"/>
     </row>
-    <row r="122" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="122" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J122" s="7"/>
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
@@ -8743,7 +8743,7 @@
       <c r="BE122" s="7"/>
       <c r="BF122" s="7"/>
     </row>
-    <row r="123" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="123" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J123" s="7"/>
       <c r="K123" s="7"/>
       <c r="L123" s="7"/>
@@ -8794,7 +8794,7 @@
       <c r="BE123" s="7"/>
       <c r="BF123" s="7"/>
     </row>
-    <row r="124" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="124" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J124" s="7"/>
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
@@ -8845,7 +8845,7 @@
       <c r="BE124" s="7"/>
       <c r="BF124" s="7"/>
     </row>
-    <row r="125" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="125" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J125" s="7"/>
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
@@ -8896,7 +8896,7 @@
       <c r="BE125" s="7"/>
       <c r="BF125" s="7"/>
     </row>
-    <row r="126" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="126" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J126" s="7"/>
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
@@ -8947,7 +8947,7 @@
       <c r="BE126" s="7"/>
       <c r="BF126" s="7"/>
     </row>
-    <row r="127" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="127" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J127" s="7"/>
       <c r="K127" s="7"/>
       <c r="L127" s="7"/>
@@ -8998,7 +8998,7 @@
       <c r="BE127" s="7"/>
       <c r="BF127" s="7"/>
     </row>
-    <row r="128" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="128" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J128" s="7"/>
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
@@ -9049,7 +9049,7 @@
       <c r="BE128" s="7"/>
       <c r="BF128" s="7"/>
     </row>
-    <row r="129" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="129" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J129" s="7"/>
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
@@ -9100,7 +9100,7 @@
       <c r="BE129" s="7"/>
       <c r="BF129" s="7"/>
     </row>
-    <row r="130" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="130" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J130" s="7"/>
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
@@ -9151,7 +9151,7 @@
       <c r="BE130" s="7"/>
       <c r="BF130" s="7"/>
     </row>
-    <row r="131" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="131" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J131" s="7"/>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
@@ -9202,7 +9202,7 @@
       <c r="BE131" s="7"/>
       <c r="BF131" s="7"/>
     </row>
-    <row r="132" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="132" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J132" s="7"/>
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
@@ -9253,7 +9253,7 @@
       <c r="BE132" s="7"/>
       <c r="BF132" s="7"/>
     </row>
-    <row r="133" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="133" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J133" s="7"/>
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
@@ -9304,7 +9304,7 @@
       <c r="BE133" s="7"/>
       <c r="BF133" s="7"/>
     </row>
-    <row r="134" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="134" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J134" s="7"/>
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
@@ -9355,7 +9355,7 @@
       <c r="BE134" s="7"/>
       <c r="BF134" s="7"/>
     </row>
-    <row r="135" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="135" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J135" s="7"/>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
@@ -9406,7 +9406,7 @@
       <c r="BE135" s="7"/>
       <c r="BF135" s="7"/>
     </row>
-    <row r="136" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="136" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J136" s="7"/>
       <c r="K136" s="7"/>
       <c r="L136" s="7"/>
@@ -9457,7 +9457,7 @@
       <c r="BE136" s="7"/>
       <c r="BF136" s="7"/>
     </row>
-    <row r="137" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="137" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J137" s="7"/>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
@@ -9508,7 +9508,7 @@
       <c r="BE137" s="7"/>
       <c r="BF137" s="7"/>
     </row>
-    <row r="138" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="138" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J138" s="7"/>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
@@ -9559,7 +9559,7 @@
       <c r="BE138" s="7"/>
       <c r="BF138" s="7"/>
     </row>
-    <row r="139" spans="10:58" x14ac:dyDescent="0.25">
+    <row r="139" spans="10:58" x14ac:dyDescent="0.3">
       <c r="J139" s="7"/>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
